--- a/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-GV.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-GV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\internlink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC6989C-73C3-4146-8C1C-66E340E4BB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE6F075-5F9A-46DD-9897-01DEA07598EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,18 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Email</t>
   </si>
   <si>
     <t>GV001</t>
-  </si>
-  <si>
-    <t>Nguyen Van A</t>
-  </si>
-  <si>
-    <t>nguyenvana@university.edu.vn</t>
   </si>
   <si>
     <t>0901234567</t>
@@ -64,12 +58,24 @@
   <si>
     <t>Mã GV</t>
   </si>
+  <si>
+    <t>htbin2806@gmail.com</t>
+  </si>
+  <si>
+    <t>Khoa</t>
+  </si>
+  <si>
+    <t>Đặng Quốc Cường</t>
+  </si>
+  <si>
+    <t>Công nghệ thông tin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -102,6 +108,22 @@
       <charset val="163"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="13"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -111,7 +133,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -135,19 +157,33 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -155,14 +191,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -463,44 +507,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.88671875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="21.88671875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <f>IF(B3="","",1)</f>
         <v>1</v>
@@ -509,16 +558,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="str">
         <f>IF(B4="","",A3+1)</f>
         <v/>
@@ -526,19 +578,21 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4" s="8"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="str">
         <f t="shared" ref="A5:A68" si="0">IF(B5="","",A4+1)</f>
         <v/>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" s="9"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -546,9 +600,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6" s="8"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -556,9 +611,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" s="8"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -566,9 +622,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8" s="6"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -576,9 +633,10 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -586,9 +644,10 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -596,9 +655,10 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -606,9 +666,10 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12" s="6"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -616,9 +677,10 @@
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -626,9 +688,10 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="6"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -636,9 +699,10 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -646,9 +710,10 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E16" s="6"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -656,9 +721,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -666,9 +732,10 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -676,9 +743,10 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -686,9 +754,10 @@
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="6"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -696,9 +765,10 @@
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -706,63 +776,64 @@
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1142,7 +1213,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
